--- a/cases/CASE-002/raw/Сита.xlsx
+++ b/cases/CASE-002/raw/Сита.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf81553be2f2e069/Рабочие файлы/Рабочий стол/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\asus\IWE\PACK-cattle-science\cases\CASE-002\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4DF75460589B3ACB72846B075844445BDEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51381E74-2119-49D2-BD20-FA851EC9B8BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C8D2A0-397D-4BE7-AE36-D45B98B7E25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>пенсильванские сита</t>
   </si>
@@ -48,6 +48,15 @@
   </si>
   <si>
     <t>2 просев</t>
+  </si>
+  <si>
+    <t>Силос</t>
+  </si>
+  <si>
+    <t>Сенаж люцерна</t>
+  </si>
+  <si>
+    <t>pef</t>
   </si>
 </sst>
 </file>
@@ -94,19 +103,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -388,11 +402,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H9"/>
+  <dimension ref="B2:H19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
@@ -407,16 +422,16 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
@@ -425,7 +440,7 @@
       <c r="C5" s="3">
         <v>11.5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <f>C5/$C$9</f>
         <v>2.1355617455896009E-2</v>
       </c>
@@ -447,7 +462,7 @@
       <c r="C6" s="3">
         <v>257</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <f t="shared" ref="D6:D8" si="0">C6/$C$9</f>
         <v>0.47725162488393685</v>
       </c>
@@ -469,7 +484,7 @@
       <c r="C7" s="3">
         <v>83</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <f t="shared" si="0"/>
         <v>0.1541318477251625</v>
       </c>
@@ -491,7 +506,7 @@
       <c r="C8" s="3">
         <v>187</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>0.34726090993500464</v>
       </c>
@@ -519,10 +534,146 @@
         <v>535</v>
       </c>
     </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
+        <v>46212</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>26</v>
+      </c>
+      <c r="D14" s="6">
+        <f>C14/$C$18</f>
+        <v>5.0583657587548639E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>9</v>
+      </c>
+      <c r="H14" s="7">
+        <f>G14/$G$18</f>
+        <v>2.057142857142857E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>355</v>
+      </c>
+      <c r="D15" s="6">
+        <f t="shared" ref="D15:D17" si="2">C15/$C$18</f>
+        <v>0.69066147859922178</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>301</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" ref="H15:H17" si="3">G15/$G$18</f>
+        <v>0.68799999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>64</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" si="2"/>
+        <v>0.1245136186770428</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="3">
+        <v>85.5</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="3"/>
+        <v>0.19542857142857142</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B17" s="3">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3">
+        <v>69</v>
+      </c>
+      <c r="D17" s="6">
+        <f t="shared" si="2"/>
+        <v>0.13424124513618677</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
+        <v>42</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="3"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <f>SUM(C14:C17)</f>
+        <v>514</v>
+      </c>
+      <c r="G18">
+        <f>SUM(G14:G17)</f>
+        <v>437.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="8">
+        <f>SUM(D14:D16)</f>
+        <v>0.86575875486381326</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="8">
+        <f>SUM(H14:H16)</f>
+        <v>0.90399999999999991</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
